--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 需求 → 元件 BOM'!$A$1:$O$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 元件標籤字典'!$A$1:$I$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 元件標籤字典'!$A$1:$I$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1834,7 +1834,7 @@
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py; Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程; Service Layer（invoice / settlement）; internal_ingest.py; WebSocket 端點; EventBusProducer; line_push_service + outbox worker; API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py; Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程; Service Layer（invoice / settlement）; internal_ingest.py; WebSocket 端點; EventBusProducer; line_push_service + outbox worker; API_SURFACE router filter; Portal Claim Guard; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -3373,7 +3373,7 @@
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Portal Claim Guard; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Portal Claim Guard; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Portal Claim Guard; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -4360,7 +4360,7 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>source_to_raw; raw_to_bronze; bronze_to_silver; storage（raw/bronze/silver）; SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py; MCP RAG server; 品牌庫 pgvector; rag_manual_chunks / case_entries; Medallion pipeline; Kafka; outbox; provenance / audit</t>
+          <t>source_to_raw; raw_to_bronze; bronze_to_silver; storage（raw/bronze/silver）; SQL/Schema*.sql; forward-only migrations; migration registry + routed apply; Audit Chain Checkpoint; platform schema; Tech DB router + mirror; core/db.py; MCP RAG server; 品牌庫 pgvector; rag_manual_chunks / case_entries; Medallion pipeline; Kafka; outbox; provenance / audit</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4555,7 +4555,7 @@
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; migration registry + routed apply; Audit Chain Checkpoint; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; migration registry + routed apply; Audit Chain Checkpoint; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; migration registry + routed apply; Audit Chain Checkpoint; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -14638,7 +14638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
@@ -15971,22 +15971,22 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Three-DB Connection Router</t>
+          <t>Portal Claim Guard</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>三庫連線路由</t>
+          <t>跨 portal token 守衛</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
+          <t>依 token 的 portal claim（或由角色推導）與部署面 ALLOWED_TOKEN_PORTALS 比對，拒絕技師、品牌、平台 token 跨面存取。</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>治理資料庫選擇與 fail-closed；不代表 production migration 或 backfill 已完成。</t>
+          <t>只隔離 API surface；同一 portal 內仍須由 role_required、租戶與資源規則決定可否存取。未設定 ALLOWED_TOKEN_PORTALS 的本機／測試環境不強制此 guard。</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -16018,22 +16018,22 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>DBPoolScopeMiddleware</t>
+          <t>Three-DB Connection Router</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫連線路由</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
+          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
+          <t>治理資料庫選擇與 fail-closed；不代表 production migration 或 backfill 已完成。</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -16065,22 +16065,22 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>DEKService + PII blind index + purge ledger</t>
+          <t>DBPoolScopeMiddleware</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>個資密鑰與清除稽核套件</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
+          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
+          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -16112,54 +16112,54 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>internal_ingest.py</t>
+          <t>DEKService + PII blind index + purge ledger</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>個資密鑰與清除稽核套件</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
+          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>只接受 fail-closed 內部憑證；不是 LINE webhook 入站門。</t>
+          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>API·INT</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>WebSocket 端點</t>
+          <t>internal_ingest.py</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -16169,44 +16169,44 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
+          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
+          <t>只接受 fail-closed 內部憑證；不是 LINE webhook 入站門。</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
+          <t>API·INT</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Redis pub/sub</t>
+          <t>WebSocket 端點</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -16216,44 +16216,44 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
+          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
+          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、API·INT、PLT·EVT</t>
+          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Redis pub/sub</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -16263,44 +16263,44 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
+          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
+          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
+          <t>API·DISP、API·INT、PLT·EVT</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>EventBusProducer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -16310,44 +16310,44 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
+          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
+          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>API·INT</t>
+          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11</t>
+          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>EventConsumerWorker</t>
+          <t>EventBusProducer</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -16357,44 +16357,44 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
+          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
+          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ、TEC·SET</t>
+          <t>API·INT</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>分散式排程</t>
+          <t>EventConsumerWorker</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -16404,44 +16404,44 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>跨實例協調 SLA、GDPR 硬刪、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
+          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
+          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、PLT·EVT</t>
+          <t>TEC·PROJ、TEC·SET</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>PG Advisory Cron Leader</t>
+          <t>分散式排程</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -16451,44 +16451,44 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
+          <t>跨實例協調 SLA、GDPR 硬刪、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
+          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>API·DISP</t>
+          <t>API·DISP、PLT·EVT</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§8</t>
+          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>line_push_service + outbox worker</t>
+          <t>PG Advisory Cron Leader</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -16498,44 +16498,44 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
+          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>推播失敗不回滾主業務寫入；不處理 LINE 入站 webhook。</t>
+          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>API·INT</t>
+          <t>API·DISP</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>守衛鏈</t>
+          <t>line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -16545,44 +16545,44 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
+          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>逐端點 deny-by-default enforce；不把前端隱藏按鈕當成安全控制。</t>
+          <t>推播失敗不回滾主業務寫入；不處理 LINE 入站 webhook。</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>API·GOV、PLT·IAM、TEC·ID</t>
+          <t>API·INT</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>core/errors.py</t>
+          <t>守衛鏈</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -16592,44 +16592,44 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
+          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
+          <t>逐端點 deny-by-default enforce；不把前端隱藏按鈕當成安全控制。</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·GOV、PLT·IAM、TEC·ID</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>core/idempotency.py</t>
+          <t>core/errors.py</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
+          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
+          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -16676,7 +16676,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Middleware</t>
+          <t>core/idempotency.py</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
+          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>不承載單一領域的核心業務規則。</t>
+          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -16723,7 +16723,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>AuthGuard</t>
+          <t>Middleware</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -16733,44 +16733,44 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
+          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
+          <t>不承載單一領域的核心業務規則。</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1–8.3</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>appMode gate</t>
+          <t>AuthGuard</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -16780,12 +16780,12 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
+          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
+          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -16817,7 +16817,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>rolePolicy</t>
+          <t>appMode gate</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -16827,22 +16827,22 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
+          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>只提供前端 UX 治理；不代替 API role_required。</t>
+          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·SHELL</t>
+          <t>WEB·SHELL</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -16852,19 +16852,19 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>api client</t>
+          <t>rolePolicy</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
+          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
+          <t>只提供前端 UX 治理；不代替 API role_required。</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
+          <t>WEB·AUD、WEB·SHELL</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -16899,39 +16899,39 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>AuthImage / AuthImageLightbox</t>
+          <t>api client</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>需認證媒體縮圖與預覽</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
+          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
+          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
+          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -16946,34 +16946,34 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1、§8.3</t>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>ConsentPanel</t>
+          <t>AuthImage / AuthImageLightbox</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>工單免責同意面板</t>
+          <t>需認證媒體縮圖與預覽</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
+          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
+          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -17005,22 +17005,22 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>ConsentPanel</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>工單免責同意面板</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
+          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
+          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -17052,7 +17052,7 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>realtime</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -17062,12 +17062,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
+          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>負責前端即時連線生命週期；不是事件持久層。</t>
+          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -17099,7 +17099,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>型別（api.generated.ts）</t>
+          <t>realtime</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
+          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
+          <t>負責前端即時連線生命週期；不是事件持久層。</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD</t>
+          <t>WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -17134,19 +17134,19 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Medallion pipeline</t>
+          <t>型別（api.generated.ts）</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -17156,44 +17156,44 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
+          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
+          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>WEB·AUD</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>source_to_raw</t>
+          <t>Medallion pipeline</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -17203,44 +17203,44 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>收集原始外部素材並原樣落地到 raw 層，保留來源識別與取得資訊。</t>
+          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
+          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.6</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1；附錄</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>raw_to_bronze</t>
+          <t>source_to_raw</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -17250,44 +17250,44 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
+          <t>收集原始外部素材並原樣落地到 raw 層，保留來源識別與取得資訊。</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
+          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
+          <t>DAT·MED</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>bronze_to_silver</t>
+          <t>raw_to_bronze</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -17297,12 +17297,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
+          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>silver 不等於已核可發布；下游仍需提煉、HITL 與 Publisher gate。</t>
+          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>storage（raw/bronze/silver）</t>
+          <t>bronze_to_silver</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -17344,44 +17344,44 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
+          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
+          <t>silver 不等於已核可發布；下游仍需提煉、HITL 與 Publisher gate。</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
+          <t>DAT·MED、REF·INTAKE</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.6</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1；附錄</t>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql</t>
+          <t>storage（raw/bronze/silver）</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -17391,17 +17391,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
+          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
+          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
+          <t>DAT·MED</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -17411,24 +17411,24 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>forward-only migrations</t>
+          <t>SQL/Schema*.sql</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -17438,12 +17438,12 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
+          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
+          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -17468,14 +17468,14 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>platform schema</t>
+          <t>forward-only migrations</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -17485,12 +17485,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
+          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>不存單一品牌內的工單、客戶或報價真相。</t>
+          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -17515,61 +17515,61 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>MCP RAG server</t>
+          <t>migration registry + routed apply</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫 migration 登記與分流套用</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
+          <t>以 migration 檔頭的 migrate-targets 將 schema 變更分流套用到品牌、技師與平台庫，並各自寫入 schema_migrations，再由 drift-check 對照登記簿。</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
+          <t>提供受控套用與可檢查性；不代表任何 production 環境已套用或資料 backfill 已完成。</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §5、§8–9</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§9.1、§11.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>品牌庫 pgvector</t>
+          <t>platform schema</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -17579,44 +17579,44 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
+          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
+          <t>不存單一品牌內的工單、客戶或報價真相。</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>DAT·RAG、REF·PUB</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>rag_manual_chunks / case_entries</t>
+          <t>MCP RAG server</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -17626,12 +17626,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
+          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
+          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -17663,7 +17663,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>outbox</t>
+          <t>品牌庫 pgvector</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -17673,44 +17673,44 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
+          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件日誌。</t>
+          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>DAT·RAG、REF·PUB</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>provenance / audit</t>
+          <t>rag_manual_chunks / case_entries</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -17720,44 +17720,44 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
+          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>不允許 LLM 自行編造來源，也不把一般顯示日誌當成不可否認稽核鏈。</t>
+          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>DAT·RAG</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>汲取層</t>
+          <t>outbox</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -17767,91 +17767,91 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
+          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
+          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件日誌。</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>REF·INTAKE</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>提煉分流器</t>
+          <t>Audit Chain Checkpoint</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>稽核雜湊鏈重基準點</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
+          <t>以受鎖保護的鏈尾快照建立 append-only checkpoint，讓 audit verify 可從已核准的歷史基準後驗證並回報所有後續斷點。</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>只產生 draft；未經 HITL 核可不得寫入 pgvector 或 Skill。</t>
+          <t>只處理既有歷史鏈的非破壞式 re-baseline；不修正未來寫入流程，也不取代 audit event 的內容完整性驗證。</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>REF·REFINE</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（服務已落地，部署流程未完整）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Draft Queue</t>
+          <t>provenance / audit</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -17861,44 +17861,44 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
+          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>是待審產物，不是已發布知識。</t>
+          <t>不允許 LLM 自行編造來源，也不把一般顯示日誌當成不可否認稽核鏈。</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL、REF·REFINE</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已落地，部署流程未完整）</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>審核 UI backend</t>
+          <t>汲取層</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -17908,22 +17908,22 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的 HITL 後端。</t>
+          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
+          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL</t>
+          <t>REF·INTAKE</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -17933,19 +17933,19 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Casdoor reviewer auth</t>
+          <t>提煉分流器</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -17955,22 +17955,22 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
+          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
+          <t>只產生 draft；未經 HITL 核可不得寫入 pgvector 或 Skill。</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL</t>
+          <t>REF·REFINE</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
+          <t>PARTIAL（服務已落地，部署流程未完整）</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -17980,19 +17980,19 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Draft Queue</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -18002,22 +18002,22 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/artifact。</t>
+          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人審 gate。</t>
+          <t>是待審產物，不是已發布知識。</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>REF·HITL、REF·REFINE</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已落地，部署流程未完整）</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -18027,19 +18027,19 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>behavior patch artifact</t>
+          <t>審核 UI backend</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -18049,22 +18049,22 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>行為軌核可後產生 target_path + content 的受控 artifact，保存於 draft provenance，交由 apply CLI 消費。</t>
+          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的 HITL 後端。</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>artifact 仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git fallback 才生效。</t>
+          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>REF·HITL</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -18074,19 +18074,19 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>LiveSkill DB ingest</t>
+          <t>Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -18096,22 +18096,22 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>apply_behavior 預設呼叫 internal skills ingest，將核可 artifact 以加性合併建立品牌 skill draft，再由後台人工發布。</t>
+          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git fallback。</t>
+          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>REF·HITL</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -18121,19 +18121,19 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>self-service routers</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -18143,44 +18143,44 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/artifact。</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人審 gate。</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>technician_service</t>
+          <t>behavior patch artifact</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -18190,44 +18190,44 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+          <t>行為軌核可後產生 target_path + content 的受控 artifact，保存於 draft provenance，交由 apply CLI 消費。</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+          <t>artifact 仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git fallback 才生效。</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>certification/kyc_service</t>
+          <t>LiveSkill DB ingest</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -18237,44 +18237,44 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+          <t>apply_behavior 預設呼叫 internal skills ingest，將核可 artifact 以加性合併建立品牌 skill draft，再由後台人工發布。</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>未核可或已失效認證不得進入媒合候選集。</t>
+          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git fallback。</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>lock_tech</t>
+          <t>self-service routers</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -18321,7 +18321,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>OHS API routers</t>
+          <t>technician_service</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -18331,22 +18331,22 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -18356,19 +18356,19 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>schedule_service</t>
+          <t>certification/kyc_service</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -18378,22 +18378,22 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+          <t>未核可或已失效認證不得進入媒合候選集。</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -18403,19 +18403,19 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>事件層</t>
+          <t>lock_tech</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -18425,44 +18425,44 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+          <t>不存各品牌的完整工單或客戶敏感資料。</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH、TEC·PROJ</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>technician_workorder_projection</t>
+          <t>OHS API routers</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -18472,44 +18472,44 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
+          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
+          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ</t>
+          <t>TEC·MATCH</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>技師工單 read-model</t>
+          <t>schedule_service</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -18519,44 +18519,44 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌全量敏感資料。</t>
+          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ</t>
+          <t>TEC·MATCH</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>technician_commission_projection</t>
+          <t>事件層</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -18566,44 +18566,44 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
+          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
+          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
+          <t>TEC·MATCH、TEC·PROJ</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>technician settlement services</t>
+          <t>technician_workorder_projection</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -18613,27 +18613,27 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
+          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已落地。</t>
+          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
+          <t>TEC·PROJ</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§9</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -18643,61 +18643,61 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Tech DB router + mirror</t>
+          <t>技師工單 read-model</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>技師權威庫路由與相容鏡射</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
+          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
+          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌全量敏感資料。</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH、TEC·ID</t>
+          <t>TEC·PROJ</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Casdoor</t>
+          <t>technician_commission_projection</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -18707,44 +18707,44 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>發行身分與角色資訊；資源層授權仍由各 API deny-by-default enforce。</t>
+          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·SET</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>License Entitlement Gate</t>
+          <t>technician settlement services</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -18754,91 +18754,91 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應 fail-closed。</t>
+          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>是應用層授權檢查；不等於部署 per-brand bundle 的 provisioning 自動化。</t>
+          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已落地。</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·SET</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>平台維運 console</t>
+          <t>Tech DB router + mirror</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>技師權威庫路由與相容鏡射</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>DAT·SCH、TEC·ID</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>License provisioning</t>
+          <t>Casdoor</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -18848,12 +18848,12 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+          <t>發行身分與角色資訊；資源層授權仍由各 API deny-by-default enforce。</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -18885,7 +18885,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>SigNoz</t>
+          <t>License Entitlement Gate</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -18895,44 +18895,44 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與告警。</t>
+          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應 fail-closed。</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+          <t>是應用層授權檢查；不等於部署 per-brand bundle 的 provisioning 自動化。</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>OPIK</t>
+          <t>平台維運 console</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -18942,44 +18942,44 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>專注 AI 調用品質；不代替 SigNoz 的全系統可觀測性。</t>
+          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>OpenTelemetry</t>
+          <t>License provisioning</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -18989,44 +18989,44 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>PIIScrubSpanProcessor</t>
+          <t>SigNoz</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -19036,12 +19036,12 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與告警。</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -19073,7 +19073,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Flow DSL executor</t>
+          <t>OPIK</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -19083,44 +19083,44 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+          <t>專注 AI 調用品質；不代替 SigNoz 的全系統可觀測性。</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>domain blocks / primitives</t>
+          <t>OpenTelemetry</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -19130,44 +19130,44 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Vertical Pack</t>
+          <t>PIIScrubSpanProcessor</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -19177,44 +19177,44 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>可版本化的產業配置包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG、PLT·FLOW</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>FlowEditor</t>
+          <t>Flow DSL executor</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -19224,44 +19224,44 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及 HITL gate。</t>
+          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>PLT·FLOW</t>
+          <t>API·WO、PLT·FLOW</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>TO-BE（M4 設計）</t>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>待 M4 實作；目前為 SDS 設計元件</t>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry</t>
+          <t>domain blocks / primitives</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -19271,44 +19271,44 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央配置能力。</t>
+          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>租戶只可改客製層；安全、金額、工具白名單等保護層不可 override。</t>
+          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>API·WO、PLT·FLOW</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>M18 Config Registry</t>
+          <t>Vertical Pack</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -19318,22 +19318,22 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>已落地的配置服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+          <t>可版本化的產業配置包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>只涵蓋現行 M18 配置能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>PLT·CFG、PLT·FLOW</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -19343,19 +19343,19 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Skill Revision Registry</t>
+          <t>FlowEditor</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -19365,22 +19365,22 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及 HITL gate。</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>PLT·FLOW</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>TO-BE（M4 設計）</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -19390,64 +19390,205 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
+          <t>Agent Configuration Studio / Config Registry</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央配置能力。</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>租戶只可改客製層；安全、金額、工具白名單等保護層不可 override。</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>M18 Config Registry</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>已落地的配置服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>只涵蓋現行 M18 配置能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Skill Revision Registry</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
           <t>HITL 審核骨架</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>共用的 draft→diff→人審→核可/駁回→發布模式，同時支援知識精煉與 AI Onboarding Compiler。</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>AI 只產生 draft；高風險知識或流程未人審不得落地。</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>PLT·CFG</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>12_SAD §9</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I102"/>
+  <autoFilter ref="A1:I105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 需求 → 元件 BOM'!$A$1:$O$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 元件標籤字典'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 元件標籤字典'!$A$1:$I$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14638,7 +14638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14702,168 +14702,168 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>line_gateway</t>
+          <t>Mutation contract</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>LINE 通道閘道</t>
+          <t>前端安全寫入契約</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派文字/照片/postback，並將文字與核准圖片回覆送回 LINE。</t>
+          <t>前端 mutation 的共同執行約定：依風險選擇 optimistic 或 server-confirmed，並統一 rollback、精準 cache invalidation、stable action/idempotency key 與 409 conflict 處理。</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>只負責通道整合與旁路轉發；不負責主要 AI 推理、定價或開工單。</t>
+          <t>只治理前端寫入體驗與失敗復原；不取代後端授權、狀態機、冪等與資料庫交易。</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN</t>
+          <t>WEB·OPS</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT（Notification mark-read pilot）</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.3、§14</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>web/shared-contract/src/mutation.ts; web/brand-portal/src/components/layout/NotificationDrawer.tsx</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Photo Guide resolver</t>
+          <t>user_preferences</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>品牌照片樣本圖解析器</t>
+          <t>跨裝置使用者偏好</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>解析 AI 回覆文末的 photo-guide 標記、剝除內部標記並按設定附加 LINE ImageMessage；目前只核准 Chatlock 安裝前樣本圖。</t>
+          <t>依品牌、技師、平台三個權威庫保存需要跨裝置同步的偏好；以 tenant + principal 隔離、key allowlist、大小上限與 version CAS 控制寫入。</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>只呈現預先核准的品牌靜態圖片；不讀取或辨識客戶照片，也不允許未設定品牌自行附圖。</t>
+          <t>不保存登入憑證或敏感業務資料；theme、locale 等裝置偏好仍可留在瀏覽器本機。</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN</t>
+          <t>API·GOV、WEB·SHELL</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT（migration 120）</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.2–§4.3、§14</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §6.1、§8.1</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>SQL/migrations/120-user-preferences.sql; api/{routers/preferences,services/preference_service}.py; web/brand-portal/src/lib/preferences.ts</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Quote postback message mapper</t>
+          <t>Command Palette</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>報價回覆錯誤話術分類器</t>
+          <t>Ctrl/⌘+K 指令導覽</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>依 QUOTE_EXPIRED、QUOTE_ALREADY_DECIDED、NOT_FOUND、FORBIDDEN 等 API error_code 產生對客戶可理解的 LINE 回覆。</t>
+          <t>由 registry 宣告 route、required capability 與 context 的高頻導覽介面，依目前使用者可見能力篩選命令。</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>只映射終態與錯誤話術；報價狀態機、權限與冪等仍由品牌 API 執行。</t>
+          <t>只改善功能發現性與操作效率；前端顯示條件不授予任何後端 API 權限。</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN</t>
+          <t>WEB·SHELL</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT（Brand Portal pilot）</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.3、§14</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>web/brand-portal/src/components/layout/CommandPalette.tsx; web/brand-portal/src/lib/commandRegistry.ts</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>WebhookIdempotencyStore</t>
+          <t>Resource ownership matrix</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>LINE webhook 冪等保留庫</t>
+          <t>資源歸屬授權矩陣</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>在處理 LINE event 前以 mark-first 方式保留 event ID，重送時直接略過，避免重複回覆或建卡。</t>
+          <t>將 mutation 與敏感 read/export 對應到品牌、技師、平台、public capability 或 internal service owner contract，並列出必跑的負向租戶測試。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>只治理 webhook 重播；不代替報價、工單與金流 mutation 的 Idempotency-Key。</t>
+          <t>是可機讀治理與測試索引；不取代 router/service 的 tenant、role、capability 與資料隸屬守衛。</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -14873,232 +14873,232 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.2、§14</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §6.1</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>api/core/resource_ownership.py; api/tests/test_cr_0190_resource_ownership_matrix.py</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>AgentLoop</t>
+          <t>Service principal / credential</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>LockCore runtime（產品層）</t>
+          <t>機器身分／可撤銷服務憑證</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
+          <t>給 workload 使用的非真人身分與憑證生命週期：hash-only、audience/scope/tenant、到期、輪替重疊窗、撤銷與稽核。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
+          <t>不得與真人 OIDC session 混用；新憑證驗證失敗不得降級成 legacy internal token。</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·RES</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT；production bootstrap／legacy fallback 歸零待部署證據</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.2、§14</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §6.1–§6.4</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>SQL/migrations/121-service-principal-credentials.sql; api/{services/service_credential_service,routers/platform_service_principals}.py; api/core/deps.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>AgentRunner</t>
+          <t>Job registry / worker runtime</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>LockCore runtime（通用執行層）</t>
+          <t>背景工作清冊／獨立執行核心</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
+          <t>以 code-defined registry 管理 14 個背景工作的 owner、schedule、冪等、lock、retry、補償與 SLI，並由獨立 worker 或 Cloud Run Job 執行。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
+          <t>不在 API request path 偷跑慢工作；registry 宣告也不等於 production worker 已完成切換。</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
+          <t>API·INT、PLT·EVT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT；production cutover 待部署證據</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+          <t>12_SAD §4.2、§8、§14</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+          <t>15_SDS §6.3</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>api/realtime/job_registry.py; api/worker_main.py; scripts/deploy/worker-job.sh</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ReplyGuard</t>
+          <t>Release manifest</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>發版稽核清單</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Agent 回覆出口守衛：攔截確定金額、錯誤型號、假稱已轉真人等違規輸出，必要時重生或轉人工。</t>
+          <t>每次 staging／production promotion 保存 commit、immutable image digest、revision、migration、config/secret reference、health/evidence 與 rollback 資訊的可驗證工件。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>是模型輸出的最後安全層；不取代 API 的報價、派工與權限硬閘。</t>
+          <t>只保存機密參照而不保存 secret 值；manifest 生成成功不等於 smoke、rollback 或 restore drill 已通過。</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
+          <t>PLT·CFG（Release）</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT workflow；staging／production 證據待外部環境</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §8、§14</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §11</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>.github/workflows/cloud-run-deploy.yml; scripts/release/{release_manifest,validate_release_manifest,rollback_release,verify_rollback_drill}.py</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>SentimentClassifier</t>
+          <t>web/shared-contract</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>四站窄共享契約套件</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>在不阻斷主回覆的前提下判定負面情緒並產生告警所需資料。</t>
+          <t>四個前端共用的無 UI 契約套件，集中 runtime OpenAPI types、RFC7807、mutation/conflict、capability 與 session 契約，並以 immutable vendored tarball 固定版本。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>只做情緒分類與旁路告警；不單獨決定報價、派工或工單狀態。</t>
+          <t>禁止放 React UI、theme、i18n、route policy 或領域流程；各站仍維持獨立部署與產品邊界。</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
+          <t>WEB·SHELL、WEB·OPS、WEB·AUD、WEB·CX</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT（0.1.0）</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.3、§14</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>web/shared-contract/; scripts/ci/{generate-api-types,vendor-shared-contract}.sh; .github/workflows/shared-contract.yml</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>ContextBuilder</t>
+          <t>line_gateway</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>LockCore runtime（上下文層）</t>
+          <t>LINE 通道閘道</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
+          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派文字/照片/postback，並將文字與核准圖片回覆送回 LINE。</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
+          <t>只負責通道整合與旁路轉發；不負責主要 AI 推理、定價或開工單。</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
+          <t>AGT·CHN</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -15113,39 +15113,39 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>LiteLLMProvider + FallbackProvider</t>
+          <t>Photo Guide resolver</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>品牌照片樣本圖解析器</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
+          <t>解析 AI 回覆文末的 photo-guide 標記、剝除內部標記並按設定附加 LINE ImageMessage；目前只核准 Chatlock 安裝前樣本圖。</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>處理模型調用、重試與 failover；不承載業務規則或產品決策。</t>
+          <t>只呈現預先核准的品牌靜態圖片；不讀取或辨識客戶照片，也不允許未設定品牌自行附圖。</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>AGT·GOV、PLT·LLM</t>
+          <t>AGT·CHN</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -15155,44 +15155,44 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.2、§5.1、§13 ｜ 15_SDS §5.1、§5.4</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer</t>
+          <t>Quote postback message mapper</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>報價回覆錯誤話術分類器</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>供應商無關的模型編排層：集中管理路由、fallback、逾時、快取與調用效率。</t>
+          <t>依 QUOTE_EXPIRED、QUOTE_ALREADY_DECIDED、NOT_FOUND、FORBIDDEN 等 API error_code 產生對客戶可理解的 LINE 回覆。</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
+          <t>只映射終態與錯誤話術；報價狀態機、權限與冪等仍由品牌 API 執行。</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>PLT·LLM</t>
+          <t>AGT·CHN</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -15202,44 +15202,44 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.2、§5.1、§13</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ToolRegistry</t>
+          <t>WebhookIdempotencyStore</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LINE webhook 冪等保留庫</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Agent 工具登錄與白名單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
+          <t>在處理 LINE event 前以 mark-first 方式保留 event ID，重送時直接略過，避免重複回覆或建卡。</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
+          <t>只治理 webhook 重播；不代替報價、工單與金流 mutation 的 Idempotency-Key。</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·RES</t>
+          <t>AGT·CHN</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -15249,44 +15249,44 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>MemoryManager + Store</t>
+          <t>AgentLoop</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>LockCore runtime（產品層）</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id；預設 SQLite，可配置 PostgreSQL。</t>
+          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
+          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
+          <t>AGT·CHN、AGT·RES</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -15301,39 +15301,39 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>EscalationStore</t>
+          <t>AgentRunner</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（通用執行層）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
+          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>保證轉人事件不蒸發；不是正式工單庫，也不代替 API 的開單 gate。</t>
+          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
+          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -15343,71 +15343,71 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§5.3</t>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SkillsLoader + 2 builtin skills</t>
+          <t>ReplyGuard</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與紅線。</t>
+          <t>Agent 回覆出口守衛：攔截確定金額、錯誤型號、假稱已轉真人等違規輸出，必要時重生或轉人工。</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
+          <t>是模型輸出的最後安全層；不取代 API 的報價、派工與權限硬閘。</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
+          <t>AGT·RES</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9 ｜ 12_SAD §4.4</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 ｜ 15_SDS §5.1、§5.4 ｜ 15_SDS §9.1、§9.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>SkillSync</t>
+          <t>SentimentClassifier</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -15417,17 +15417,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>輪詢品牌庫已發布的 skill revision，以原子交換同步到 workspace overlay，讓新版本在執行期生效。</t>
+          <t>在不阻斷主回覆的前提下判定負面情緒並產生告警所需資料。</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>只同步已發布版本且失敗時保留舊版；不自行核准 draft，也不覆寫平台保護層。</t>
+          <t>只做情緒分類與旁路告警；不單獨決定報價、派工或工單狀態。</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
+          <t>AGT·RES</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -15442,34 +15442,34 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>記憶 DB</t>
+          <t>ContextBuilder</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Memory backend</t>
+          <t>LockCore runtime（上下文層）</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
+          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
+          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -15501,7 +15501,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>tenant-scoped routers</t>
+          <t>LiteLLMProvider + FallbackProvider</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -15511,17 +15511,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
+          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
+          <t>處理模型調用、重試與 failover；不承載業務規則或產品決策。</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>API·CASE</t>
+          <t>AGT·GOV、PLT·LLM</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -15531,24 +15531,24 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§4.6、§6.1</t>
+          <t>15_SDS §2.2、§5.1、§13 ｜ 15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Service Layer（problem_card / quote）</t>
+          <t>Model Orchestration Layer</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -15558,17 +15558,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
+          <t>供應商無關的模型編排層：集中管理路由、fallback、逾時、快取與調用效率。</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
+          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>API·CASE</t>
+          <t>PLT·LLM</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -15578,44 +15578,44 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§4.6、§6.1</t>
+          <t>15_SDS §2.2、§5.1、§13</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
+          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Conversation media collector</t>
+          <t>ToolRegistry</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>對話照片掛卡器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>AI 建問題卡時反查同一對話近 24 小時內最多 5 張照片，依時間排序附加到 media_urls。</t>
+          <t>Agent 工具登錄與白名單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>只掛接已持久化媒體 URL，採 append-only 且查詢失敗略過；不做任何影像辨識。</t>
+          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>API·CASE</t>
+          <t>AGT·GOV、AGT·RES</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -15625,44 +15625,44 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§4.6、§6.1</t>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）</t>
+          <t>MemoryManager + Store</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
+          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id；預設 SQLite，可配置 PostgreSQL。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>不允許 AI 繞過客戶確認與 HITL 直接轉工單。</t>
+          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>API·WO</t>
+          <t>AGT·KNW</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -15672,44 +15672,44 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Consent link service</t>
+          <t>EscalationStore</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>免責同意簽署連結服務</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>為工單產生公開簽署 token、保存 token hash 稽核並透過 LINE 推送；無 LINE 綁定時回傳可複製連結。</t>
+          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>只負責交付簽署入口與稽核；簽署內容、角色/租戶授權與結案 gate 仍由 API 驗證。</t>
+          <t>保證轉人事件不蒸發；不是正式工單庫，也不代替 API 的開單 gate。</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>API·WO</t>
+          <t>AGT·RES</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -15719,165 +15719,165 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）</t>
+          <t>SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
+          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與紅線。</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
+          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>API·DISP</t>
+          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
+          <t>AS-BUILT ｜ PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§8</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9 ｜ 12_SAD §4.4</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §5.1 ｜ 15_SDS §5.1、§5.4 ｜ 15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>dispatch_service candidate scoring</t>
+          <t>SkillSync</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>現行媒合評分器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>現行派工服務直接由技師權威資料評估技能、品牌授權、距離、評分、工作量與公平性，產生候選排序。</t>
+          <t>輪詢品牌庫已發布的 skill revision，以原子交換同步到 workspace overlay，讓新版本在執行期生效。</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>這是共用 API codebase 的 interim 實作；目標 OHS/MatchingService 獨立服務邊界尚未拆出。</t>
+          <t>只同步已發布版本且失敗時保留舊版；不自行核准 draft，也不覆寫平台保護層。</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、TEC·MATCH</t>
+          <t>AGT·KNW</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/ ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Service Layer（invoice / settlement）</t>
+          <t>記憶 DB</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory backend</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
+          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
+          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>API·FIN</t>
+          <t>AGT·KNW</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§6.1、§7.3</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>core/db.py</t>
+          <t>tenant-scoped routers</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -15887,111 +15887,111 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>API 資料庫基礎層：管理品牌庫、技師權威庫與平台庫的連線取得、交易邊界及安全 fallback。</t>
+          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>不放領域流程決策；業務交易應由 service 層調用。</t>
+          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
+          <t>API·CASE</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6 ｜ 12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1 ｜ 15_SDS §4.2、§4.6、§6.1 ｜ 15_SDS §4.2、§6.1、§7.3</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>API_SURFACE router filter</t>
+          <t>Service Layer（problem_card / quote）</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>API 部署面塑形器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>同一 FastAPI codebase 依 API_SURFACE=dispatch/tech/platform 裁切路由與背景 worker，形成三個可獨立部署面。</t>
+          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>只縮小部署暴露面，不是授權邊界；每個保留端點仍須 RBAC、租戶或平台守衛。</t>
+          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>API·GOV、TEC·ID</t>
+          <t>API·CASE</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Portal Claim Guard</t>
+          <t>Conversation media collector</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>跨 portal token 守衛</t>
+          <t>對話照片掛卡器</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>依 token 的 portal claim（或由角色推導）與部署面 ALLOWED_TOKEN_PORTALS 比對，拒絕技師、品牌、平台 token 跨面存取。</t>
+          <t>AI 建問題卡時反查同一對話近 24 小時內最多 5 張照片，依時間排序附加到 media_urls。</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>只隔離 API surface；同一 portal 內仍須由 role_required、租戶與資源規則決定可否存取。未設定 ALLOWED_TOKEN_PORTALS 的本機／測試環境不強制此 guard。</t>
+          <t>只掛接已持久化媒體 URL，採 append-only 且查詢失敗略過；不做任何影像辨識。</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·CASE</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -16001,44 +16001,44 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Three-DB Connection Router</t>
+          <t>Service Layer（work_order）</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>三庫連線路由</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
+          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>治理資料庫選擇與 fail-closed；不代表 production migration 或 backfill 已完成。</t>
+          <t>不允許 AI 繞過客戶確認與 HITL 直接轉工單。</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·WO</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -16053,39 +16053,39 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>DBPoolScopeMiddleware</t>
+          <t>Consent link service</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免責同意簽署連結服務</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
+          <t>為工單產生公開簽署 token、保存 token hash 稽核並透過 LINE 推送；無 LINE 綁定時回傳可複製連結。</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
+          <t>只負責交付簽署入口與稽核；簽署內容、角色/租戶授權與結案 gate 仍由 API 驗證。</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·WO</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -16100,113 +16100,113 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>DEKService + PII blind index + purge ledger</t>
+          <t>Service Layer（dispatch）</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>個資密鑰與清除稽核套件</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
+          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
+          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·DISP</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>internal_ingest.py</t>
+          <t>dispatch_service candidate scoring</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>現行媒合評分器</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
+          <t>現行派工服務直接由技師權威資料評估技能、品牌授權、距離、評分、工作量與公平性，產生候選排序。</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>只接受 fail-closed 內部憑證；不是 LINE webhook 入站門。</t>
+          <t>這是共用 API codebase 的 interim 實作；目標 OHS/MatchingService 獨立服務邊界尚未拆出。</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>API·INT</t>
+          <t>API·DISP、TEC·MATCH</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11</t>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/ ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>WebSocket 端點</t>
+          <t>Service Layer（invoice / settlement）</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -16216,44 +16216,44 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
+          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
+          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
+          <t>API·FIN</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Redis pub/sub</t>
+          <t>core/db.py</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -16263,185 +16263,185 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
+          <t>API 資料庫基礎層：管理品牌庫、技師權威庫與平台庫的連線取得、交易邊界及安全 fallback。</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
+          <t>不放領域流程決策；業務交易應由 service 層調用。</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、API·INT、PLT·EVT</t>
+          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>AS-BUILT ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6 ｜ 12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1 ｜ 15_SDS §4.2、§4.6、§6.1 ｜ 15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>API_SURFACE router filter</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>API 部署面塑形器</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
+          <t>同一 FastAPI codebase 依 API_SURFACE=dispatch/tech/platform 裁切路由與背景 worker，形成三個可獨立部署面。</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
+          <t>只縮小部署暴露面，不是授權邊界；每個保留端點仍須 RBAC、租戶或平台守衛。</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
+          <t>API·GOV、TEC·ID</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>EventBusProducer</t>
+          <t>Portal Claim Guard</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>跨 portal token 守衛</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
+          <t>依 token 的 portal claim（或由角色推導）與部署面 ALLOWED_TOKEN_PORTALS 比對，拒絕技師、品牌、平台 token 跨面存取。</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
+          <t>只隔離 API surface；同一 portal 內仍須由 role_required、租戶與資源規則決定可否存取。未設定 ALLOWED_TOKEN_PORTALS 的本機／測試環境不強制此 guard。</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>API·INT</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1–6.3、§11</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>EventConsumerWorker</t>
+          <t>Three-DB Connection Router</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫連線路由</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
+          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
+          <t>治理資料庫選擇與 fail-closed；不代表 production migration 或 backfill 已完成。</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ、TEC·SET</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>分散式排程</t>
+          <t>DBPoolScopeMiddleware</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -16451,91 +16451,91 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>跨實例協調 SLA、GDPR 硬刪、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
+          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
+          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>API·DISP、PLT·EVT</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>PG Advisory Cron Leader</t>
+          <t>DEKService + PII blind index + purge ledger</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>個資密鑰與清除稽核套件</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
+          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
+          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>API·DISP</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§8</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.3、§11.1</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>line_push_service + outbox worker</t>
+          <t>internal_ingest.py</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -16545,12 +16545,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
+          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>推播失敗不回滾主業務寫入；不處理 LINE 入站 webhook。</t>
+          <t>只接受 fail-closed 內部憑證；不是 LINE webhook 入站門。</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -16582,7 +16582,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>守衛鏈</t>
+          <t>WebSocket 端點</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -16592,44 +16592,44 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
+          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>逐端點 deny-by-default enforce；不把前端隱藏按鈕當成安全控制。</t>
+          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>API·GOV、PLT·IAM、TEC·ID</t>
+          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>core/errors.py</t>
+          <t>Redis pub/sub</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -16639,44 +16639,44 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
+          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
+          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·DISP、API·INT、PLT·EVT</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>core/idempotency.py</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -16686,44 +16686,44 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
+          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
+          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Middleware</t>
+          <t>EventBusProducer</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -16733,44 +16733,44 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
+          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>不承載單一領域的核心業務規則。</t>
+          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>API·GOV</t>
+          <t>API·INT</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§6.4</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>AuthGuard</t>
+          <t>EventConsumerWorker</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -16780,44 +16780,44 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
+          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
+          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
+          <t>TEC·PROJ、TEC·SET</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1–8.3</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>appMode gate</t>
+          <t>分散式排程</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -16827,44 +16827,44 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
+          <t>跨實例協調 SLA、GDPR 硬刪、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
+          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
+          <t>API·DISP、PLT·EVT</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1–8.3</t>
+          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>rolePolicy</t>
+          <t>PG Advisory Cron Leader</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -16874,44 +16874,44 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
+          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>只提供前端 UX 治理；不代替 API role_required。</t>
+          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·SHELL</t>
+          <t>API·DISP</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>api client</t>
+          <t>line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -16921,111 +16921,111 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
+          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
+          <t>推播失敗不回滾主業務寫入；不處理 LINE 入站 webhook。</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
+          <t>API·INT</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>AuthImage / AuthImageLightbox</t>
+          <t>守衛鏈</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>需認證媒體縮圖與預覽</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
+          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
+          <t>逐端點 deny-by-default enforce；不把前端隱藏按鈕當成安全控制。</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
+          <t>API·GOV、PLT·IAM、TEC·ID</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1、§8.3</t>
+          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>ConsentPanel</t>
+          <t>core/errors.py</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>工單免責同意面板</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
+          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
+          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -17035,24 +17035,24 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1、§8.3</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>core/idempotency.py</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -17062,17 +17062,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
+          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
+          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -17082,24 +17082,24 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1、§8.3</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>realtime</t>
+          <t>Middleware</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
+          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>負責前端即時連線生命週期；不是事件持久層。</t>
+          <t>不承載單一領域的核心業務規則。</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
+          <t>API·GOV</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -17129,24 +17129,24 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.3</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1、§8.3</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>型別（api.generated.ts）</t>
+          <t>AuthGuard</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -17156,22 +17156,22 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
+          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
+          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>WEB·AUD</t>
+          <t>WEB·SHELL</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -17181,19 +17181,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §8.1</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Medallion pipeline</t>
+          <t>appMode gate</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -17203,44 +17203,44 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
+          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
+          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>WEB·SHELL</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>source_to_raw</t>
+          <t>rolePolicy</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -17250,44 +17250,44 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>收集原始外部素材並原樣落地到 raw 層，保留來源識別與取得資訊。</t>
+          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
+          <t>只提供前端 UX 治理；不代替 API role_required。</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
+          <t>WEB·AUD、WEB·SHELL</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1；附錄</t>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>raw_to_bronze</t>
+          <t>api client</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -17297,111 +17297,111 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
+          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
+          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
+          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>bronze_to_silver</t>
+          <t>AuthImage / AuthImageLightbox</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>需認證媒體縮圖與預覽</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
+          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>silver 不等於已核可發布；下游仍需提煉、HITL 與 Publisher gate。</t>
+          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
+          <t>WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>storage（raw/bronze/silver）</t>
+          <t>ConsentPanel</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>工單免責同意面板</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
+          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
+          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
+          <t>WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -17411,24 +17411,24 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1；附錄</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -17438,17 +17438,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
+          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
+          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
+          <t>WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -17458,24 +17458,24 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>forward-only migrations</t>
+          <t>realtime</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -17485,17 +17485,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
+          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
+          <t>負責前端即時連線生命週期；不是事件持久層。</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
+          <t>WEB·CX、WEB·OPS</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -17505,44 +17505,44 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>migration registry + routed apply</t>
+          <t>型別（api.generated.ts）</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>三庫 migration 登記與分流套用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>以 migration 檔頭的 migrate-targets 將 schema 變更分流套用到品牌、技師與平台庫，並各自寫入 schema_migrations，再由 drift-check 對照登記簿。</t>
+          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>提供受控套用與可檢查性；不代表任何 production 環境已套用或資料 backfill 已完成。</t>
+          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
+          <t>WEB·AUD</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -17552,24 +17552,24 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>platform schema</t>
+          <t>Medallion pipeline</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -17579,44 +17579,44 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
+          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>不存單一品牌內的工單、客戶或報價真相。</t>
+          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>MCP RAG server</t>
+          <t>source_to_raw</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -17626,44 +17626,44 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
+          <t>收集原始外部素材並原樣落地到 raw 層，保留來源識別與取得資訊。</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
+          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
+          <t>DAT·MED</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §5、§8–9</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§9.1、§11.3</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>品牌庫 pgvector</t>
+          <t>raw_to_bronze</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -17673,44 +17673,44 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
+          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
+          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>DAT·RAG、REF·PUB</t>
+          <t>DAT·MED、REF·INTAKE</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>rag_manual_chunks / case_entries</t>
+          <t>bronze_to_silver</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -17720,44 +17720,44 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
+          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
+          <t>silver 不等於已核可發布；下游仍需提煉、HITL 與 Publisher gate。</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
+          <t>DAT·MED、REF·INTAKE</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §5、§8–9</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §5.1、§9.1、§11.3</t>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>outbox</t>
+          <t>storage（raw/bronze/silver）</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -17767,59 +17767,59 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
+          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件日誌。</t>
+          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>DAT·MED</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Audit Chain Checkpoint</t>
+          <t>SQL/Schema*.sql</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>稽核雜湊鏈重基準點</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>以受鎖保護的鏈尾快照建立 append-only checkpoint，讓 audit verify 可從已核准的歷史基準後驗證並回報所有後續斷點。</t>
+          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>只處理既有歷史鏈的非破壞式 re-baseline；不修正未來寫入流程，也不取代 audit event 的內容完整性驗證。</t>
+          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -17851,7 +17851,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>provenance / audit</t>
+          <t>forward-only migrations</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -17861,91 +17861,91 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
+          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>不允許 LLM 自行編造來源，也不把一般顯示日誌當成不可否認稽核鏈。</t>
+          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.6、§8.2</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>汲取層</t>
+          <t>migration registry + routed apply</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫 migration 登記與分流套用</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
+          <t>以 migration 檔頭的 migrate-targets 將 schema 變更分流套用到品牌、技師與平台庫，並各自寫入 schema_migrations，再由 drift-check 對照登記簿。</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
+          <t>提供受控套用與可檢查性；不代表任何 production 環境已套用或資料 backfill 已完成。</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>REF·INTAKE</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>提煉分流器</t>
+          <t>platform schema</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -17955,44 +17955,44 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
+          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>只產生 draft；未經 HITL 核可不得寫入 pgvector 或 Skill。</t>
+          <t>不存單一品牌內的工單、客戶或報價真相。</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>REF·REFINE</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（服務已落地，部署流程未完整）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Draft Queue</t>
+          <t>MCP RAG server</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -18002,44 +18002,44 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
+          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>是待審產物，不是已發布知識。</t>
+          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL、REF·REFINE</t>
+          <t>DAT·RAG</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已落地，部署流程未完整）</t>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>審核 UI backend</t>
+          <t>品牌庫 pgvector</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -18049,44 +18049,44 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的 HITL 後端。</t>
+          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
+          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL</t>
+          <t>DAT·RAG、REF·PUB</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2</t>
+          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Casdoor reviewer auth</t>
+          <t>rag_manual_chunks / case_entries</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -18096,44 +18096,44 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
+          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
+          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>REF·HITL</t>
+          <t>DAT·RAG</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1–9.2</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>outbox</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -18143,91 +18143,91 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/artifact。</t>
+          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人審 gate。</t>
+          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件日誌。</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>behavior patch artifact</t>
+          <t>Audit Chain Checkpoint</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>稽核雜湊鏈重基準點</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>行為軌核可後產生 target_path + content 的受控 artifact，保存於 draft provenance，交由 apply CLI 消費。</t>
+          <t>以受鎖保護的鏈尾快照建立 append-only checkpoint，讓 audit verify 可從已核准的歷史基準後驗證並回報所有後續斷點。</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>artifact 仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git fallback 才生效。</t>
+          <t>只處理既有歷史鏈的非破壞式 re-baseline；不修正未來寫入流程，也不取代 audit event 的內容完整性驗證。</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>DAT·SCH</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>LiveSkill DB ingest</t>
+          <t>provenance / audit</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -18237,44 +18237,44 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>apply_behavior 預設呼叫 internal skills ingest，將核可 artifact 以加性合併建立品牌 skill draft，再由後台人工發布。</t>
+          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git fallback。</t>
+          <t>不允許 LLM 自行編造來源，也不把一般顯示日誌當成不可否認稽核鏈。</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
+          <t>DAT·SYNC</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.4</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §9.1、§9.3</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>self-service routers</t>
+          <t>汲取層</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -18284,44 +18284,44 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·INTAKE</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>technician_service</t>
+          <t>提煉分流器</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -18331,44 +18331,44 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+          <t>只產生 draft；未經 HITL 核可不得寫入 pgvector 或 Skill。</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·REFINE</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（服務已落地，部署流程未完整）</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>certification/kyc_service</t>
+          <t>Draft Queue</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -18378,44 +18378,44 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>未核可或已失效認證不得進入媒合候選集。</t>
+          <t>是待審產物，不是已發布知識。</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·HITL、REF·REFINE</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已落地，部署流程未完整）</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>lock_tech</t>
+          <t>審核 UI backend</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -18425,44 +18425,44 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的 HITL 後端。</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
+          <t>REF·HITL</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>OHS API routers</t>
+          <t>Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -18472,44 +18472,44 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
+          <t>REF·HITL</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>schedule_service</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -18519,44 +18519,44 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/artifact。</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人審 gate。</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>事件層</t>
+          <t>behavior patch artifact</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -18566,44 +18566,44 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+          <t>行為軌核可後產生 target_path + content 的受控 artifact，保存於 draft provenance，交由 apply CLI 消費。</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+          <t>artifact 仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git fallback 才生效。</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>TEC·MATCH、TEC·PROJ</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>technician_workorder_projection</t>
+          <t>LiveSkill DB ingest</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -18613,44 +18613,44 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
+          <t>apply_behavior 預設呼叫 internal skills ingest，將核可 artifact 以加性合併建立品牌 skill draft，再由後台人工發布。</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
+          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git fallback。</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ</t>
+          <t>REF·PUB</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為 fallback）</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>技師工單 read-model</t>
+          <t>self-service routers</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -18660,44 +18660,44 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌全量敏感資料。</t>
+          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>TEC·PROJ</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§8.2</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>technician_commission_projection</t>
+          <t>technician_service</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -18707,44 +18707,44 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
+          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
+          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>technician settlement services</t>
+          <t>certification/kyc_service</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -18754,91 +18754,91 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
+          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已落地。</t>
+          <t>未核可或已失效認證不得進入媒合候選集。</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.5、§9</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §7.1、§7.3、§11.1</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Tech DB router + mirror</t>
+          <t>lock_tech</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>技師權威庫路由與相容鏡射</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
+          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
+          <t>不存各品牌的完整工單或客戶敏感資料。</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>DAT·SCH、TEC·ID</t>
+          <t>TEC·ID</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Casdoor</t>
+          <t>OHS API routers</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -18848,44 +18848,44 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>發行身分與角色資訊；資源層授權仍由各 API deny-by-default enforce。</t>
+          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·MATCH</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>License Entitlement Gate</t>
+          <t>schedule_service</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -18895,44 +18895,44 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應 fail-closed。</t>
+          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>是應用層授權檢查；不等於部署 per-brand bundle 的 provisioning 自動化。</t>
+          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·MATCH</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>平台維運 console</t>
+          <t>事件層</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -18942,44 +18942,44 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·MATCH、TEC·PROJ</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已落地；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>License provisioning</t>
+          <t>technician_workorder_projection</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -18989,44 +18989,44 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
+          <t>TEC·PROJ</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3、§9</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§6.1、§11.2</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>SigNoz</t>
+          <t>技師工單 read-model</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -19036,44 +19036,44 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與告警。</t>
+          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌全量敏感資料。</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>TEC·PROJ</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>OPIK</t>
+          <t>technician_commission_projection</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -19083,44 +19083,44 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>專注 AI 調用品質；不代替 SigNoz 的全系統可觀測性。</t>
+          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>TEC·SET</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>OpenTelemetry</t>
+          <t>technician settlement services</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -19130,91 +19130,91 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已落地。</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>TEC·SET</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>PIIScrubSpanProcessor</t>
+          <t>Tech DB router + mirror</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>技師權威庫路由與相容鏡射</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
+          <t>DAT·SCH、TEC·ID</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §8.2、§9</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §12</t>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py; api/services/audit_log_service.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Flow DSL executor</t>
+          <t>Casdoor</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -19224,44 +19224,44 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+          <t>發行身分與角色資訊；資源層授權仍由各 API deny-by-default enforce。</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>domain blocks / primitives</t>
+          <t>License Entitlement Gate</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -19271,44 +19271,44 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應 fail-closed。</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+          <t>是應用層授權檢查；不等於部署 per-brand bundle 的 provisioning 自動化。</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Vertical Pack</t>
+          <t>平台維運 console</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -19318,44 +19318,44 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>可版本化的產業配置包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG、PLT·FLOW</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>FlowEditor</t>
+          <t>License provisioning</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -19365,44 +19365,44 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及 HITL gate。</t>
+          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>PLT·FLOW</t>
+          <t>PLT·IAM</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>TO-BE（M4 設計）</t>
+          <t>PARTIAL（Casdoor/config 存在；provisioning 未完整）</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>待 M4 實作；目前為 SDS 設計元件</t>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry</t>
+          <t>SigNoz</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -19412,44 +19412,44 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央配置能力。</t>
+          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與告警。</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>租戶只可改客製層；安全、金額、工具白名單等保護層不可 override。</t>
+          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>M18 Config Registry</t>
+          <t>OPIK</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -19459,44 +19459,44 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>已落地的配置服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>只涵蓋現行 M18 配置能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+          <t>專注 AI 調用品質；不代替 SigNoz 的全系統可觀測性。</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Skill Revision Registry</t>
+          <t>OpenTelemetry</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
@@ -19506,89 +19506,465 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
+          <t>PLT·OBS</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>12_SAD §9</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>15_SDS §3.2、§10、§13</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
+          <t>PIIScrubSpanProcessor</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已落地；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Flow DSL executor</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>domain blocks / primitives</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Vertical Pack</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>可版本化的產業配置包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>FlowEditor</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及 HITL gate。</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="inlineStr">
+        <is>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Agent Configuration Studio / Config Registry</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央配置能力。</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>租戶只可改客製層；安全、金額、工具白名單等保護層不可 override。</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>M18 Config Registry</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>已落地的配置服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>只涵蓋現行 M18 配置能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Skill Revision Registry</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I112" s="7" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
           <t>HITL 審核骨架</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>共用的 draft→diff→人審→核可/駁回→發布模式，同時支援知識精煉與 AI Onboarding Compiler。</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>AI 只產生 draft；高風險知識或流程未人審不得落地。</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>PLT·CFG</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>PARTIAL（M18/LiveSkill 已落地；完整 Studio 未完成）</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>12_SAD §9</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
+      <c r="I113" s="7" t="inlineStr">
         <is>
           <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分落地）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
+  <autoFilter ref="A1:I113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>怎麼下手</t>
@@ -523,19 +523,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>② 是 L1 子系統 → L2 能力群 → L3 需求的三層樹（Excel 群組可摺疊）。先看 L2 的 Code reality 找出 PARTIAL/TO-BE 的能力群，再展開該群的 L3。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+          <t>② 是 L1 Epic（子系統）→ L2 Feature（能力群）→ L3 Story/Quality requirement（需求）的三層樹（Excel 群組可摺疊）。先看 L2 的 Code reality 找出 PARTIAL/TO-BE 的能力群，再展開該群的 L3。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>L2 不是 join key</t>
+          <t>L1/L2 是真的卡，但不是 join key</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L1/L2 是顯示分群，唯一主鍵是 L3 的 FR / NFR ID。任何跨表對照都用 ID，不要用 L2 名稱。</t>
+          <t>這兩件事要分開：①「它們在 Plane 是真的 work item」（8 張 Epic、32 張 Feature），有 parent 鏈、有沿鏈 roll-up 的覆蓋率數字，不再只是 Excel 上的顯示分群；②「唯一主鍵仍是 L3 的 FR / NFR ID」——L2 代號帶「（顯示）」尾綴就是這個意思，任何跨表對照一律用 ID，不要用 L2 名稱當鍵。</t>
         </is>
       </c>
     </row>
@@ -602,126 +602,238 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>Story 不等於「User Story」</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>守則的 Story 是「需求層級的身分」（level 2，契約掛這裡），不是敏捷慣用的價值切片協商佔位符。FR 說「系統該有什麼」，User Story 說「這個迭代要做出什麼」——本專案沒有後者那一層，價值敘述由旅程（SC）＋Persona＋BDD 承載，硬加一層 story 只是多一份要人維護的映射。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>「目標里程碑」為什麼只有一個值</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Plane 的 Issue.milestone 是單值。原本的 M1/M2/M3+ 三欄容得下 M1→M3 這種區間，單值欄位容不下，所以取區間的**終點**（交付檢查點問的是「到這關驗完了沒」）。起點不丟——完整區間保留在「節點範圍」欄。目前有 5 條 FR 是跨節點的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Issue.milestone 是單值。原本的 M1/M2/M3+ 三欄容得下 M1→M3 這種區間，單值欄位容不下，所以取區間的「終點」（交付檢查點問的是「到這關驗完了沒」）。起點不丟——完整區間保留在「節點範圍」欄。目前有 5 條 FR 是跨節點的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>NFR 的「目標里程碑」為什麼是空的</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>106 條 NFR 目前一條都沒有節點歸屬，代表每一道驗收閘都不含任何非功能需求。這是已知缺口，要靠「NFR 驗證形態」分類後才能決定哪幾條進閘門、哪幾條走持續量測。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>「NFR 驗證形態」怎麼讀</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>分類軸是「證據從哪來」，不是「屬於哪個品質類別」——同一個 Security 需求，寫成「TLS 1.2+」是可掃描的，寫成「租戶隔離設計正確」就只能審查。所以先問證據來源。① 門檻量測（k6/benchmark，有數值）與 ② 掃描（SAST/SCA/axe）進 case 庫、可自動化；③ 審查（checklist/ADR）與 ④ 持續 SLO（生產量測/演練）出貨前根本測不了，走 ReleaseEvidence。硬把 ④ 做成 test case，會得到一個每天「執行」卻不代表任何測試的假 case。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>標「⚠ 跨形態」的要怎麼辦</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>那條需求的驗證方式同時橫跨兩種形態（例如「secret scan + audit」＝掃描＋審查）。守則要求拆成兩條需求分開寫——混在一條的結果是其中一半永遠驗不了，而閘門看不出來少了什麼。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>「ReleaseEvidence key」給誰用</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>形態 ③④ 的證據要登錄成 Plane 的 release evidence，平台以 (專案, key) upsert，所以 key 必須穩定，重複送出才會更新同一列而不是長出重複。⚠️ 這個端點只在內部 API，API 金鑰打不進去——只能人工在 Plane 網頁上輸入。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-    </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>黃色欄位</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>灰色欄位</t>
+          <t>Plane 詞彙對照</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>白色欄位</t>
+          <t xml:space="preserve">  L1 Epic</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>正典敘述，同樣改上游。</t>
+          <t>Plane 的 Epic（work item type，level 0，is_epic=true）。8 張：7 個子系統 ＋ NFR 全域品質地板。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  L2 Feature</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Feature（level 1）。32 張能力群。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>四個狀態軸不得互推</t>
+          <t xml:space="preserve">  L3 ＝ Story</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+          <t>FR 在 Plane 是 Story（level 2）。「驗收契約掛在這一層」，上面兩層的數字都是繼承來的。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  L3 ＝ Quality requirement</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NFR 在 Plane 是 Quality requirement，「與 Story 同階、不是子層」。NFR 橫跨所有層級，做成子層會逼它選一個歸屬，而「Feature 層的效能要求」就無處可放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WBS 工作包</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Task（level 3），列在《規格統控規劃書》③。它是工程任務，不是 User Story。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  服務旅程</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Scenario 卡（SC）。它不在本表的三層樹上——旅程橫跨多個子系統，掛不進單一 parent，改為直接持有自己的驗收契約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  子系統 / 能力群</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>同時是兩件事：在「拆解軸」是 Epic/Feature 卡（本表的 L1/L2），在「排程軸」是 Plane 的 Module（範疇分組）。兩軸正交，不是同一個東西的兩個名字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>黃色欄位</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>白色欄位</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>正典敘述，同樣改上游。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>四個狀態軸不得互推</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -741,7 +853,7 @@
   <dimension ref="A1:R212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -856,7 +968,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -865,7 +977,11 @@
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
           <t>agent（LockCore AI 客服）</t>
@@ -900,7 +1016,7 @@
       <c r="L2" s="4" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr"/>
@@ -920,7 +1036,7 @@
     <row r="3" outlineLevel="1" ht="22" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -933,7 +1049,11 @@
           <t>agent</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>通道與 Turn 編排</t>
@@ -968,7 +1088,7 @@
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
@@ -1240,7 +1360,7 @@
     <row r="7" outlineLevel="1" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1253,7 +1373,11 @@
           <t>agent</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>診斷與轉真人</t>
@@ -1288,7 +1412,7 @@
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
@@ -1644,7 +1768,7 @@
     <row r="12" outlineLevel="1" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1657,7 +1781,11 @@
           <t>agent</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>記憶與知識</t>
@@ -1692,7 +1820,7 @@
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
@@ -1880,7 +2008,7 @@
     <row r="15" outlineLevel="1" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1893,7 +2021,11 @@
           <t>agent</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>AI 邊界治理</t>
@@ -1928,7 +2060,7 @@
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
@@ -2116,7 +2248,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2125,7 +2257,11 @@
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>api（派工營運控制平面）</t>
@@ -2160,7 +2296,7 @@
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr"/>
@@ -2180,7 +2316,7 @@
     <row r="19" outlineLevel="1" ht="22" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2193,7 +2329,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>問題卡與報價</t>
@@ -2228,7 +2368,7 @@
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
@@ -2668,7 +2808,7 @@
     <row r="25" outlineLevel="1" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2681,7 +2821,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>工單與現場</t>
@@ -2716,7 +2860,7 @@
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
@@ -2988,7 +3132,7 @@
     <row r="29" outlineLevel="1" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3001,7 +3145,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>派工與 SLA</t>
@@ -3036,7 +3184,7 @@
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
@@ -3308,7 +3456,7 @@
     <row r="33" outlineLevel="1" ht="22" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3321,7 +3469,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>付款與結算</t>
@@ -3356,7 +3508,7 @@
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -3628,7 +3780,7 @@
     <row r="37" outlineLevel="1" ht="22" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3641,7 +3793,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>內部整合與即時通道</t>
@@ -3676,7 +3832,7 @@
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3948,7 +4104,7 @@
     <row r="41" outlineLevel="1" ht="22" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3961,7 +4117,11 @@
           <t>api</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>隱私與例外審批</t>
@@ -3996,7 +4156,7 @@
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -4184,7 +4344,7 @@
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4193,7 +4353,11 @@
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
           <t>web（多站前端）</t>
@@ -4228,7 +4392,7 @@
       <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr"/>
@@ -4248,7 +4412,7 @@
     <row r="45" outlineLevel="1" ht="22" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4261,7 +4425,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>入口、權限與降級</t>
@@ -4296,7 +4464,7 @@
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -4568,7 +4736,7 @@
     <row r="49" outlineLevel="1" ht="22" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4581,7 +4749,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>派工營運與報表</t>
@@ -4616,7 +4788,7 @@
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4804,7 +4976,7 @@
     <row r="52" outlineLevel="1" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4817,7 +4989,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>稽核治理</t>
@@ -4852,7 +5028,7 @@
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4956,7 +5132,7 @@
     <row r="54" outlineLevel="1" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -4969,7 +5145,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
           <t>消費者 LIFF</t>
@@ -5004,7 +5184,7 @@
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -5108,7 +5288,7 @@
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -5117,7 +5297,11 @@
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
           <t>data-pipeline（資料與 schema）</t>
@@ -5152,7 +5336,7 @@
       <c r="L56" s="4" t="inlineStr"/>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr"/>
@@ -5172,7 +5356,7 @@
     <row r="57" outlineLevel="1" ht="22" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5185,7 +5369,11 @@
           <t>data-pipeline</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Medallion 知識資料</t>
@@ -5220,7 +5408,7 @@
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -5324,7 +5512,7 @@
     <row r="59" outlineLevel="1" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5337,7 +5525,11 @@
           <t>data-pipeline</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Schema 與 migration</t>
@@ -5372,7 +5564,7 @@
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -5560,7 +5752,7 @@
     <row r="62" outlineLevel="1" ht="22" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5573,7 +5765,11 @@
           <t>data-pipeline</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
           <t>向量語料</t>
@@ -5608,7 +5804,7 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5712,7 +5908,7 @@
     <row r="64" outlineLevel="1" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5725,7 +5921,11 @@
           <t>data-pipeline</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>同步與稽核基座</t>
@@ -5760,7 +5960,7 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5948,7 +6148,7 @@
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -5957,7 +6157,11 @@
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>knowledge-refinery（知識精煉）</t>
@@ -5992,7 +6196,7 @@
       <c r="L67" s="4" t="inlineStr"/>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr"/>
@@ -6012,7 +6216,7 @@
     <row r="68" outlineLevel="1" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6025,7 +6229,11 @@
           <t>knowledge-refinery</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
           <t>素材汲取</t>
@@ -6060,7 +6268,7 @@
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -6164,7 +6372,7 @@
     <row r="70" outlineLevel="1" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6177,7 +6385,11 @@
           <t>knowledge-refinery</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>LLM 提煉分流</t>
@@ -6212,7 +6424,7 @@
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -6316,7 +6528,7 @@
     <row r="72" outlineLevel="1" ht="22" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6329,7 +6541,11 @@
           <t>knowledge-refinery</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
           <t>HITL 審核</t>
@@ -6364,7 +6580,7 @@
       <c r="L72" s="5" t="inlineStr"/>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -6552,7 +6768,7 @@
     <row r="75" outlineLevel="1" ht="22" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -6565,7 +6781,11 @@
           <t>knowledge-refinery</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Publisher 雙路落地</t>
@@ -6600,7 +6820,7 @@
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6704,7 +6924,7 @@
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6713,7 +6933,11 @@
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
           <t>technician-platform（技師共享池）</t>
@@ -6748,7 +6972,7 @@
       <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr"/>
@@ -6768,7 +6992,7 @@
     <row r="78" outlineLevel="1" ht="22" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -6781,7 +7005,11 @@
           <t>technician-platform</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
           <t>身分、KYC 與生命週期</t>
@@ -6816,7 +7044,7 @@
       <c r="L78" s="5" t="inlineStr"/>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -7088,7 +7316,7 @@
     <row r="82" outlineLevel="1" ht="22" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -7101,7 +7329,11 @@
           <t>technician-platform</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
           <t>OHS 媒合與接單</t>
@@ -7136,7 +7368,7 @@
       <c r="L82" s="5" t="inlineStr"/>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -7408,7 +7640,7 @@
     <row r="86" outlineLevel="1" ht="22" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -7421,7 +7653,11 @@
           <t>technician-platform</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
           <t>工單投影</t>
@@ -7456,7 +7692,7 @@
       <c r="L86" s="5" t="inlineStr"/>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr"/>
@@ -7560,7 +7796,7 @@
     <row r="88" outlineLevel="1" ht="22" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -7573,7 +7809,11 @@
           <t>technician-platform</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
           <t>技師結算</t>
@@ -7608,7 +7848,7 @@
       <c r="L88" s="5" t="inlineStr"/>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr"/>
@@ -7712,7 +7952,7 @@
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -7721,7 +7961,11 @@
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
           <t>00_platform（平台整合層）</t>
@@ -7756,7 +8000,7 @@
       <c r="L90" s="4" t="inlineStr"/>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr"/>
@@ -7776,7 +8020,7 @@
     <row r="91" outlineLevel="1" ht="22" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -7789,7 +8033,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
           <t>身分、RBAC 與 License</t>
@@ -7824,7 +8072,7 @@
       <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N91" s="5" t="inlineStr"/>
@@ -8096,7 +8344,7 @@
     <row r="95" outlineLevel="1" ht="22" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -8109,7 +8357,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
           <t>事件與即時骨幹</t>
@@ -8144,7 +8396,7 @@
       <c r="L95" s="5" t="inlineStr"/>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N95" s="5" t="inlineStr"/>
@@ -8248,7 +8500,7 @@
     <row r="97" outlineLevel="1" ht="22" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -8261,7 +8513,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
           <t>模型編排</t>
@@ -8296,7 +8552,7 @@
       <c r="L97" s="5" t="inlineStr"/>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N97" s="5" t="inlineStr"/>
@@ -8400,7 +8656,7 @@
     <row r="99" outlineLevel="1" ht="22" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -8413,7 +8669,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr"/>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
           <t>可觀測性</t>
@@ -8448,7 +8708,7 @@
       <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr"/>
@@ -8552,7 +8812,7 @@
     <row r="101" outlineLevel="1" ht="22" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -8565,7 +8825,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr"/>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
           <t>工單積木引擎</t>
@@ -8600,7 +8864,7 @@
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N101" s="5" t="inlineStr"/>
@@ -8704,7 +8968,7 @@
     <row r="103" outlineLevel="1" ht="22" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2 Feature</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -8717,7 +8981,11 @@
           <t>00_platform</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr"/>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
           <t>Agent 配置與平台治理</t>
@@ -8752,7 +9020,7 @@
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>能力群（非 join key）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr"/>
@@ -8940,7 +9208,7 @@
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1 Epic</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -8949,7 +9217,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
           <t>全域品質地板（非功能需求）</t>
@@ -8988,7 +9260,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>子系統</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N106" s="4" t="inlineStr"/>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>A11y 品質地板</t>
+          <t>可及性地板</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Aud 品質地板</t>
+          <t>稽核性地板</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Avail 品質地板</t>
+          <t>可用性地板</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Comp 品質地板</t>
+          <t>合規地板</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>DORA 品質地板</t>
+          <t>交付效能地板</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>DQ 品質地板</t>
+          <t>資料品質地板</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Maint 品質地板</t>
+          <t>可維護性地板</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Obs 品質地板</t>
+          <t>可觀測性地板</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>PUB 品質地板</t>
+          <t>知識發布地板</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Perf 品質地板</t>
+          <t>效能地板</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Priv 品質地板</t>
+          <t>隱私地板</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Rel 品質地板</t>
+          <t>可靠性地板</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Rep 品質地板</t>
+          <t>可重現性地板</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>SLA 品質地板</t>
+          <t>服務等級地板</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Scal 品質地板</t>
+          <t>可擴展性地板</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Sch 品質地板</t>
+          <t>Schema 演進地板</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Sec 品質地板</t>
+          <t>安全性地板</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_模組功能BOM.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 需求 → 元件 BOM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 元件標籤字典" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="② 需求 → 元件 BOM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③ 元件標籤字典" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 需求 → 元件 BOM'!$A$1:$S$216</definedName>
